--- a/InputData/trans/BVTQaZ/BAU Veh Techs Qualifying as ZEVs.xlsx
+++ b/InputData/trans/BVTQaZ/BAU Veh Techs Qualifying as ZEVs.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28712"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\trans\BVTQaZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{722D1444-26BF-CD48-BC52-2BDB6B88BE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2AD9286-9179-4878-9659-9E7C87A6D6AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F45BA27-DC7A-4400-8BDD-B3010FD2094A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33340" yWindow="4520" windowWidth="28800" windowHeight="15600" firstSheet="1" xr2:uid="{7166B4F5-29DF-47A7-8501-7E54D22AC689}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="3" activeTab="6" xr2:uid="{7166B4F5-29DF-47A7-8501-7E54D22AC689}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="BVTQaZ" sheetId="2" r:id="rId2"/>
+    <sheet name="BVTQaZ-LDVs" sheetId="2" r:id="rId2"/>
+    <sheet name="BVTQaZ-HDVs" sheetId="7" r:id="rId3"/>
+    <sheet name="BVTQaZ-aircraft" sheetId="6" r:id="rId4"/>
+    <sheet name="BVTQaZ-rail" sheetId="5" r:id="rId5"/>
+    <sheet name="BVTQaZ-ships" sheetId="4" r:id="rId6"/>
+    <sheet name="BVTQaZ-motorbikes" sheetId="3" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,30 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>BVTQaZ BAU Vehicle Technologies Qualifying as ZEVs</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="15">
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Mexico's NDC</t>
-  </si>
-  <si>
-    <t>SEMARNAT</t>
-  </si>
-  <si>
-    <t>https://www.gob.mx/cms/uploads/attachment/file/937518/06_2024.ACTUALIZACI_N_DE_LA_CONTRIBUCI_N_DETERMINADA_A_NIVEL_NACIONAL_190624_Rev2.pdf</t>
-  </si>
-  <si>
-    <t>pg. 30 Electromobility strategy points to electric and plug-in hybrid vehicles</t>
-  </si>
-  <si>
-    <t>Estrategia de mitigación Ventas de vehículos eléctricos e híbridos enchufables</t>
-  </si>
-  <si>
-    <t>Unit: boolean</t>
+    <t>hydrogen vehicle</t>
   </si>
   <si>
     <t>battery electric vehicle</t>
@@ -81,14 +68,32 @@
     <t>LPG vehicle</t>
   </si>
   <si>
-    <t>hydrogen vehicle</t>
+    <t>Unit: boolean</t>
+  </si>
+  <si>
+    <t>BVTQaZ BAU Vehicle Technologies Qualifying as ZEVs</t>
+  </si>
+  <si>
+    <t>Mexico's NDC</t>
+  </si>
+  <si>
+    <t>SEMARNAT</t>
+  </si>
+  <si>
+    <t>https://www.gob.mx/cms/uploads/attachment/file/937518/06_2024.ACTUALIZACI_N_DE_LA_CONTRIBUCI_N_DETERMINADA_A_NIVEL_NACIONAL_190624_Rev2.pdf</t>
+  </si>
+  <si>
+    <t>pg. 30 Electromobility strategy points to electric and plug-in hybrid vehicles</t>
+  </si>
+  <si>
+    <t>Estrategia de mitigación Ventas de vehículos eléctricos e híbridos enchufables</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,9 +170,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -188,9 +193,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,7 +233,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -334,7 +339,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -476,7 +481,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -485,52 +490,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C5140B-A3FA-4DAF-B6D3-27BA9BD40705}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="51.42578125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B4" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B5" s="5">
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" s="6" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{27D0C1A1-F478-4826-850F-29D7E74395D0}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{235888AB-1806-4C08-9463-CAE355228F8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -543,14 +545,14 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AZ8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -706,9 +708,9 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:52">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -864,9 +866,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:52">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1022,9 +1024,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:52">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1180,9 +1182,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1338,9 +1340,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1496,9 +1498,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:52">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1654,9 +1656,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1817,173 +1819,6402 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EDCB297-CFBF-40EF-B9D6-01AA1938CA73}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AZ8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817B9AE7-400E-42A1-A658-6C93FFA8A311}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AZ8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
-    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29612E15-1C93-4627-843E-8219C3220F67}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AZ8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AA2B587-70C1-4078-B554-C36FF61866C9}"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7727D32E-5813-40B0-A843-07A3A5963E91}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AZ8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E29BE76B-41FB-4164-93DF-93820B5D6164}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640CEBED-C66C-4463-B1B0-4AC8D3CFD940}"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C59BC70-DB17-41C6-993A-0AB202F22A99}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:AZ8"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="22.40625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
+        <v>2021</v>
+      </c>
+      <c r="D1">
+        <v>2022</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+      <c r="F1">
+        <v>2024</v>
+      </c>
+      <c r="G1">
+        <v>2025</v>
+      </c>
+      <c r="H1">
+        <v>2026</v>
+      </c>
+      <c r="I1">
+        <v>2027</v>
+      </c>
+      <c r="J1">
+        <v>2028</v>
+      </c>
+      <c r="K1">
+        <v>2029</v>
+      </c>
+      <c r="L1">
+        <v>2030</v>
+      </c>
+      <c r="M1">
+        <v>2031</v>
+      </c>
+      <c r="N1">
+        <v>2032</v>
+      </c>
+      <c r="O1">
+        <v>2033</v>
+      </c>
+      <c r="P1">
+        <v>2034</v>
+      </c>
+      <c r="Q1">
+        <v>2035</v>
+      </c>
+      <c r="R1">
+        <v>2036</v>
+      </c>
+      <c r="S1">
+        <v>2037</v>
+      </c>
+      <c r="T1">
+        <v>2038</v>
+      </c>
+      <c r="U1">
+        <v>2039</v>
+      </c>
+      <c r="V1">
+        <v>2040</v>
+      </c>
+      <c r="W1">
+        <v>2041</v>
+      </c>
+      <c r="X1">
+        <v>2042</v>
+      </c>
+      <c r="Y1">
+        <v>2043</v>
+      </c>
+      <c r="Z1">
+        <v>2044</v>
+      </c>
+      <c r="AA1">
+        <v>2045</v>
+      </c>
+      <c r="AB1">
+        <v>2046</v>
+      </c>
+      <c r="AC1">
+        <v>2047</v>
+      </c>
+      <c r="AD1">
+        <v>2048</v>
+      </c>
+      <c r="AE1">
+        <v>2049</v>
+      </c>
+      <c r="AF1">
+        <v>2050</v>
+      </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>